--- a/content/data-to-fill.xlsx
+++ b/content/data-to-fill.xlsx
@@ -9,11 +9,10 @@
   <sheets>
     <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="① 회사 기본정보" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="② 그룹 개요·연혁" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="③ 지표(계열사·ESG·IR)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="② 계열사 사업·제품" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="③ 지표 · IR" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="④ 자료·파일" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="⑤ 채용 공고" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="⑥ 계열사 소개(선택)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,8 +56,17 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="009AA6A0"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -72,7 +80,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E4F0E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE3D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EAF6F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFEDE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,8 +142,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -487,16 +522,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="118" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>컬리버 그룹 웹사이트 — 실제 데이터 입력 양식</t>
+          <t>컬리버 그룹 웹사이트 — 데이터 입력 양식 (v2, 자료 반영 후 갱신)</t>
         </is>
       </c>
     </row>
@@ -506,7 +541,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>이 파일은 현재 사이트에 '예시 / 준비 중 / 000-0000-0000'처럼 임시로 들어가 있는 값을 한곳에 모은 목록입니다.</t>
+          <t>제공해주신 자료(제품DB·IR)로 상당 부분을 이미 사이트에 반영했습니다. 이 양식은 '무엇이 반영됐고, 무엇이 아직 필요한지'를 한눈에 보여주도록 갱신했습니다.</t>
         </is>
       </c>
     </row>
@@ -516,28 +551,28 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>사용법</t>
+          <t>상태 표시</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1. 각 탭의 '✍️ 채워주실 값'(하늘색 칸)에 실제 정보를 적어주세요. 모르거나 아직 없는 항목은 비워두시면 그대로 '준비 중'으로 남습니다.</t>
+          <t>• 반영됨 (초록) — 주신 자료로 이미 사이트에 적용된 항목입니다. 확인만 해주세요. 수정이 필요하면 '채워주실 값'에 적어주세요.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2. '현재 값'과 '항목' 열은 어디를 고치는지 찾는 기준이니 수정하지 마세요.</t>
+          <t>• 필요 (주황) — 자료에 없어 아직 비어 있거나 '준비 중'인 항목입니다. 이걸 우선 채워주세요.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>3. 다 채운 파일을 전달해주시면 코드에 반영해 사이트를 다시 생성합니다.</t>
+          <t>• 선택 (회색) — 있으면 더 좋은 보완 항목입니다.</t>
         </is>
       </c>
     </row>
@@ -547,69 +582,52 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>우선순위</t>
+          <t>사용법</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>① 회사 기본정보 — 이메일·전화·주소·사업자등록번호는 지금 명백한 임시값(000-0000-0000 등)이라 가장 먼저 필요합니다.</t>
+          <t>1. '필요'(주황) 항목의 하늘색 '✍️ 채워주실 값' 칸을 먼저 채워주세요.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>② 그룹 개요·연혁 — 설립연도, 각 계열사 합류 시점 등 사실관계 확인.</t>
+          <t>2. '반영됨' 항목은 내용이 맞는지 확인만 하시고, 고칠 게 있을 때만 값을 적어주세요.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>③ 지표(계열사·지속가능·IR) — 실제 수치가 있으면 채우고, 없으면 비워두세요(자동으로 '준비 중' 유지).</t>
+          <t>3. 다 채운 파일을 전달해주시면 사이트에 반영합니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>④ 채용 공고 — 현재 4개는 예시입니다. 실제 공고로 교체하거나, 채용 중이 아니면 알려주세요(섹션 처리 방식 상의).</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>이 양식에 없는 것</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>뉴스는 이 파일이 아닙니다</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>• 뉴스 기사 — /admin.html 관리자 페이지에서 직접 작성·수정 (이미지 업로드·6개 언어 지원).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>뉴스룸 기사(보도자료·소식)는 /admin.html 관리자 페이지에서 직접 작성·수정·삭제합니다. 이 양식에는 포함하지 않았습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>이미지</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>대표이사 사진, 계열사/사업 이미지 등을 교체하려면 파일을 함께 전달해주세요(뉴스 이미지는 admin에서 업로드).</t>
+          <t>• 이미지 파일 — 대표이사 사진, 계열사·제품 사진 등은 파일로 함께 전달해주세요(제품DB의 이미지 파일명만 있고 실제 파일은 미첨부 상태).</t>
         </is>
       </c>
     </row>
@@ -624,27 +642,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>① 회사 기본정보 (필수)</t>
+          <t>① 회사 기본정보</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>푸터·문의 페이지 전역에 공통으로 노출됩니다. 가장 먼저 채워주세요.</t>
+          <t>푸터·문의·그룹개요 전역에 노출. ‘필요’ 항목(이메일·전화)을 우선 채워주세요.</t>
         </is>
       </c>
     </row>
@@ -661,162 +680,273 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>현재 값 (플레이스홀더)</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
+          <t>현재 값 / 반영 내용</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
           <t>✍️ 채워주실 값</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>푸터 · 문의</t>
+          <t>그룹개요·인사말</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
+          <t>대표이사</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>정석 (자료 반영)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>수정 시 기입</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>그룹개요·홈·연혁</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>설립 연도</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>2024년 (컬리버 법인설립)</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>수정 시 기입</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>푸터·문의·개요</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>본사 주소</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>전남 순천시 (자료 반영)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>상세 도로명 주소</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>번지·건물까지 주시면 정밀 표기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>푸터·문의</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>홈페이지</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>culiver.ai (자료 반영)</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>수정 시 기입</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>푸터·문의</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
           <t>대표 이메일</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>contact@culiver.co.kr</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>실제 대표 이메일</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>푸터 · 문의</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>미표기 (문의는 폼으로만)</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>예: info@culiver.ai</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>표시용 대표 이메일</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>푸터·문의</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>대표 전화</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>000-0000-0000</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>실제 대표 전화번호</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>푸터 · 문의 · 그룹개요</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>본사 주소</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>본사 주소를 입력하세요 (임시)</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>도로명 주소 전체</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>미표기</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>예: 061-000-0000</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>표시용 대표 전화</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>문의 폼 수신</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>문의 접수 이메일</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>환경변수 CONTACT_TO_EMAIL 미설정</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>폼 제출을 받을 이메일</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Vercel 환경변수로 설정</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>푸터 하단</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>사업자 정보</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>사업자 정보 · 주소는 실제 정보로 교체 (임시)</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>법인명 / 사업자등록번호 / 대표자 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>그룹소개(인사말)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>대표이사 성명</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>'컬리버 그룹 대표이사' (이름 없음)</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>대표이사 성함 (서명란에 표기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>문의 폼 수신</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>문의 접수 이메일</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>환경변수 CONTACT_TO_EMAIL 미설정</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>폼 제출을 받을 이메일 (Vercel 환경변수)</t>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>미표기</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>법인명/사업자등록번호/대표자</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>법적 표기용</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -828,27 +958,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>② 그룹 개요 · 연혁</t>
+          <t>② 계열사 사업 · 제품</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>그룹소개(About) 페이지의 개요 표와 연혁 타임라인. 사실관계를 확인해주세요.</t>
+          <t>제품DB 기준으로 반영 완료. 수신제팜만 자료가 없어 ‘준비 중’입니다.</t>
         </is>
       </c>
     </row>
@@ -865,208 +996,177 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>현재 값 (플레이스홀더)</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
+          <t>현재 값 / 반영 내용</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
           <t>✍️ 채워주실 값</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>그룹개요 표</t>
+          <t>컬리버 상세</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>그룹명</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>컬리버 그룹 · CULIVER GROUP</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>확인 또는 수정</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>사업·제품</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>통합솔루션(사료·6종 미생물·PCR진단·Shrimp365) + 제품 3종(컬리버1호·숨쉘·Shrimp365)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>보완 시 기입</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>그룹개요 표 · 홈 통계</t>
+          <t>에이엠피 상세</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>설립 연도</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>2019년 (2026년 지주 체제 전환)</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>실제 설립·지주전환 연도</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>사업·제품</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>이차전지 전구체 소재·장비/폐수처리/공조부품 + 제품 6종</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>보완 시 기입</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>홈 히어로 통계</t>
+          <t>코발티브 상세</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>핵심 숫자 4개</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>계열사 4 / 무항생제 100% / 연중생산 365 / 시작 2019</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>노출할 대표 지표 확정 (교체 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>사업·제품</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>패각콘크리트 업사이클(가구·오브제·굿즈) + 제품 6종</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>보완 시 기입</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>연혁</t>
+          <t>수신제팜 상세</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2019 — 컬리버 설립</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>육상 흰다리새우 BFT 양식 연구로 출발</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>실제 연도·사건 내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>사업·제품</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>자료 없음 → ‘준비 중’ 처리</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>사업 분야·제품·근무지 등</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>확정되면 상세 페이지 채움</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>연혁</t>
+          <t>전 계열사</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2021 — 에이엠피 합류</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>수처리·미생물 기술 내재화</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>실제 연도·내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>연혁</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>2023 — 코발티브 출범</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>굴 패각 업사이클 사업 시작</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>실제 연도·내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>연혁</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>2025 — 수신제팜 편입</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>수경재배 스마트팜·신선유통 추가</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>실제 연도·내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>연혁</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>2026 — 지주 체제 전환</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>네 사업을 지주 체제로 정렬</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>실제 연도·내용</t>
+          <t>제품 이미지</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>이미지 자리(그라디언트)만 표시</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>제품 사진 파일 전달</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>제품DB에 파일명만 있고 실물 미첨부</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1078,27 +1178,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>③ 지표 (계열사 · 지속가능경영 · IR)</t>
+          <t>③ 지표 · 투자정보(IR)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>‘예시 / 준비 중’으로 표시된 수치. 실제 값이 있으면 채우고, 없으면 비워두세요(그대로 '준비 중' 유지).</t>
+          <t>IR 자료의 실측·목표 수치는 반영 완료. 최신·정밀 수치는 보완 가능.</t>
         </is>
       </c>
     </row>
@@ -1115,300 +1216,209 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>현재 값 (플레이스홀더)</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
+          <t>현재 값 / 반영 내용</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
           <t>✍️ 채워주실 값</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>에이엠피 상세</t>
+          <t>컬리버·홈·ESG</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>누적 수주</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>예: 120건 / 연 30건 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>실측 성과</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>생존율 70% · 수질 정상화 7일 · 미생물 비용 -65% · 6종 미생물</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>갱신 시 기입</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>IR 자료 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>에이엠피 상세</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>용수 재이용률(%)</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>예: 85% 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>시장 지표</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>글로벌 양식 160조 · 국내 자급률 10%</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>갱신 시 기입</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>코발티브 상세</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>재활용 패각량</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>예: 연 500톤 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>매출 로드맵(목표)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>’25 5.5억 → ’27 58억 → ’30 271억 → ’33 730억 (목표)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>갱신 시 기입</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>‘목표치’로 명시함</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>코발티브 상세</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>친환경 인증</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>예: 환경표지 인증 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>인증·실적</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>TIPS·기업부설연구소·벤처확인·전남 청년기업·Shrimp365 상표·아쿠아포닉스 특허 등</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>추가 시 기입</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>수신제팜 상세</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>재배 면적</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>예: 3,000㎡ 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+          <t>재무 실적(매출·이익·인원)</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>미표기(목표만 표기)</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>공개 가능 시 실적 수치</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>공개 가능한 확정 실적이 있으면</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>수신제팜 상세</t>
+          <t>에이엠피·코발티브</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>연간 출하량</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>예: 연 120톤 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>지속가능경영</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>양식수 재이용률</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>실제 수치</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>지속가능경영</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>재활용 굴패각(톤)</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>실제 수치</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>지속가능경영</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>지역 일자리</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>실제 수치</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>투자정보(IR)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>연결 매출</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>준비 중</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>실제 매출액 (공개 가능 시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>투자정보(IR)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>준비 중</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>실제 영업이익 (공개 가능 시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>투자정보(IR)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>임직원 수</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>준비 중</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>실제 임직원 수</t>
-        </is>
-      </c>
+          <t>세부 성과 수치</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>핵심 지표만 표기</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>수주액·재활용량 등 있으면</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1420,14 +1430,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1440,7 +1451,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>현재 '준비 중' 버튼으로 비활성화되어 있습니다. 파일을 주시면 실제 다운로드로 연결합니다.</t>
+          <t>현재 ‘준비 중’ 버튼으로 비활성. 파일을 주시면 실제 다운로드로 연결합니다.</t>
         </is>
       </c>
     </row>
@@ -1457,93 +1468,117 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>현재 값 (플레이스홀더)</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
+          <t>현재 값 / 반영 내용</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
           <t>✍️ 채워주실 값</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
+          <t>투자정보(IR)</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>IR 자료(IR Deck)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>‘준비 중’ 비활성</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>PDF/PPT 파일</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>주신 34p IR을 게시용으로 올릴지 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>투자정보(IR)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>감사보고서</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>‘준비 중’ 비활성</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>PDF 파일</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
           <t>지속가능경영</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>지속가능경영 보고서</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>📄 (준비 중) 비활성</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>PDF 파일 전달 시 연결</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>투자정보(IR)</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>감사보고서</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>📄 (준비 중) 비활성</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>PDF 파일 전달 시 연결</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>투자정보(IR)</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>IR 자료(IR Deck)</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>📄 (준비 중) 비활성</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>PDF/PPT 파일 전달 시 연결</t>
-        </is>
-      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>‘준비 중’ 비활성</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>PDF 파일</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1555,27 +1590,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>⑤ 채용 공고 (현재 4개 모두 예시)</t>
+          <t>⑤ 채용 공고</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>실제 공고로 교체하거나, 채용 중이 아니면 알려주세요(안내 문구로 대체 가능).</t>
+          <t>직무를 실제 사업라인(양식·소재환경·제품디자인)·본사(전남 순천)로 정정 반영. 실제 공고 내용은 보완 가능.</t>
         </is>
       </c>
     </row>
@@ -1592,21 +1628,26 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>현재 값 (플레이스홀더)</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
+          <t>현재 값 / 반영 내용</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
           <t>✍️ 채워주실 값</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>채용-컬리버</t>
@@ -1614,22 +1655,27 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>직무 / 근무지</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>양식 생산 매니저 / 충남 태안 / 정규직</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>실제 직무·근무지·고용형태·직무기술서</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>양식 생산·관리 매니저</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>전남 순천 · 실제 사업 기준</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>실제 JD로 교체 시 기입</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>채용-에이엠피</t>
@@ -1637,22 +1683,27 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>직무 / 근무지</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>수처리 공정 엔지니어 / 경기 안산 / 정규직</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>실제 직무·근무지·고용형태·직무기술서</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>소재·환경 엔지니어</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>전남 순천(협의) · 실제 사업 기준</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>실제 JD로 교체 시 기입</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>채용-코발티브</t>
@@ -1660,22 +1711,27 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>직무 / 근무지</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>소재 R&amp;D 연구원 / 경남 통영 / 정규직</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>실제 직무·근무지·고용형태·직무기술서</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>제품 디자이너</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>반영됨</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>전남 순천(협의) · 실제 사업 기준</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>실제 JD로 교체 시 기입</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>채용-수신제팜</t>
@@ -1683,22 +1739,31 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>직무 / 근무지</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>스마트팜 재배 담당 / 전북 김제 / 정규직</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>실제 직무·근무지·고용형태·직무기술서</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>직무</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>‘준비 중’ 처리</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>실제 채용 직무</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>채용 시 공개</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>채용(공통)</t>
@@ -1709,180 +1774,27 @@
           <t>지원 방법</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>지원하기 → 문의 폼 프리필</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>이메일 지원/채용사이트 링크 등 원하는 방식</t>
-        </is>
-      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>이메일/채용사이트 링크 등</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>⑥ 계열사 상세 소개 (선택 보완)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>현재 소개 문구는 일반적 설명입니다. 더 정확한 내용이 있으면 보완해주세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>위치 (페이지)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>현재 값 (플레이스홀더)</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>✍️ 채워주실 값</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>컬리버 상세</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>소개·제품·기술</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>BFT 흰다리새우 스마트양식 (일반 설명)</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>실제 제품 라인업·기술 상세 (있으면)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>에이엠피 상세</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>소개·제품·기술</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>수처리·순환여과·미생물 제제 (일반 설명)</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>실제 설비·수주 사례 (있으면)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>코발티브 상세</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>소개·제품·기술</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>굴패각 업사이클 '숨쉘'·'셸픽' (일반 설명)</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>실제 제품·인증 (있으면)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>수신제팜 상세</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>소개·제품·기술</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>수경재배 스마트팜·신선유통 (일반 설명)</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>실제 작물·유통 채널 (있으면)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
